--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20232.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="74">
   <si>
     <t>Mat</t>
   </si>
@@ -103,6 +103,9 @@
     <t>PALOMARES</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>PIMENTEL</t>
   </si>
   <si>
@@ -157,6 +160,9 @@
     <t>AMADOR</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>ENRIQUEZ</t>
   </si>
   <si>
@@ -190,6 +196,9 @@
     <t>JUAN ALONSO</t>
   </si>
   <si>
+    <t>CRIZULY AMITHAI</t>
+  </si>
+  <si>
     <t>ADIEL ALONSO</t>
   </si>
   <si>
@@ -209,6 +218,9 @@
   </si>
   <si>
     <t>YASMIN</t>
+  </si>
+  <si>
+    <t>XIMENA ANALY</t>
   </si>
   <si>
     <t>ROSA EVELYN</t>
@@ -770,7 +782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -808,10 +820,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -831,10 +843,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -854,10 +866,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -877,10 +889,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -900,10 +912,10 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -923,10 +935,10 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -940,16 +952,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920058</v>
+        <v>23330051920057</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -963,16 +975,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920060</v>
+        <v>23330051920058</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -986,16 +998,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920061</v>
+        <v>23330051920060</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1009,16 +1021,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920307</v>
+        <v>23330051920061</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
         <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1032,16 +1044,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920063</v>
+        <v>23330051920307</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
         <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1055,16 +1067,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920064</v>
+        <v>23330051920063</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1078,16 +1090,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920066</v>
+        <v>23330051920064</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1101,16 +1113,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920068</v>
+        <v>23330051920066</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1124,16 +1136,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920069</v>
+        <v>23330051920067</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
         <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1147,16 +1159,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920070</v>
+        <v>23330051920068</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
         <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1170,16 +1182,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920272</v>
+        <v>23330051920069</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
         <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1193,16 +1205,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920074</v>
+        <v>23330051920070</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
         <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1216,24 +1228,70 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
+        <v>23330051920272</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920074</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
         <v>23330051920075</v>
       </c>
-      <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20">
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20232.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20232.xlsx
@@ -607,7 +607,7 @@
         <v>94.29000000000001</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
